--- a/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-sop-instance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>Classe SOP</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>JDV-SOPClass_CISIS (1.2.250.1.213.1.1.5.689)</t>
@@ -2789,13 +2792,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2830,10 +2833,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2856,13 +2859,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2913,7 +2916,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2930,10 +2933,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2956,13 +2959,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3013,7 +3016,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
